--- a/quizzes/021_gaming_modding_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/021_gaming_modding_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1218,46 +1218,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>level_design</t>
+          <t>level_editing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Level Design</t>
+          <t>Level Editing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>game_modding_type_choices</t>
+          <t>modding_language_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>level_editing</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Level Editing</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>game_modding_type_choices</t>
+          <t>modding_language_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>modding</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Modding</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>lua</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Lua</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lua</t>
+          <t>visual_basic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lua</t>
+          <t>Visual Basic</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>swift</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Swift</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>pascal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Pascal</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>visual_basic</t>
+          <t>modscript</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Visual Basic</t>
+          <t>ModScript</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>swift</t>
+          <t>game_scripting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Game Scripting</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pascal</t>
+          <t>modding</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pascal</t>
+          <t>Modding</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>modscript</t>
+          <t>level_editor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ModScript</t>
+          <t>Level Editor</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>game_scripting</t>
+          <t>scripting_language</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Game Scripting</t>
+          <t>Scripting Language</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>modding</t>
+          <t>visual_scripting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Modding</t>
+          <t>Visual Scripting</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>level_editor</t>
+          <t>level_editor_language</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Level Editor</t>
+          <t>Level Editor Language</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>scripting_language</t>
+          <t>visual_scripting_language</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scripting Language</t>
+          <t>Visual Scripting Language</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>visual_scripting</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Visual Scripting</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>level_editor_language</t>
+          <t>game_scripting_language</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Level Editor Language</t>
+          <t>Game Scripting Language</t>
         </is>
       </c>
     </row>
@@ -1575,61 +1575,10 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>visual_scripting_language</t>
+          <t>editor_scripting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
-        <is>
-          <t>Visual Scripting Language</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>modding_language_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>modding_language_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>game_scripting_language</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Game Scripting Language</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>modding_language_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>editor_scripting</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
         <is>
           <t>Editor Scripting</t>
         </is>
